--- a/it_forms/008_laptop_research_survey_template--it_forms.xlsx
+++ b/it_forms/008_laptop_research_survey_template--it_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1138,8 +1138,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1167,12 +1167,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'work'}</t>
+          <t>work</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'work'}</t>
+          <t>work</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'personal'}</t>
+          <t>personal</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'personal'}</t>
+          <t>personal</t>
         </is>
       </c>
     </row>
@@ -1201,12 +1201,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'school'}</t>
+          <t>school</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'school'}</t>
+          <t>school</t>
         </is>
       </c>
     </row>
@@ -1218,12 +1218,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'other'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -1235,12 +1235,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'dont_know'}</t>
+          <t>dont_know</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'dont know'}</t>
+          <t>dont know</t>
         </is>
       </c>
     </row>
@@ -1252,12 +1252,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'11-12_inches'}</t>
+          <t>11-12_inches</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': '11-12 inches'}</t>
+          <t>11-12 inches</t>
         </is>
       </c>
     </row>
@@ -1269,12 +1269,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'13-14_inches'}</t>
+          <t>13-14_inches</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': '13-14 inches'}</t>
+          <t>13-14 inches</t>
         </is>
       </c>
     </row>
@@ -1286,12 +1286,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'15-16_inches'}</t>
+          <t>15-16_inches</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': '15-16 inches'}</t>
+          <t>15-16 inches</t>
         </is>
       </c>
     </row>
@@ -1303,12 +1303,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'17-18_inches'}</t>
+          <t>17-18_inches</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': '17-18 inches'}</t>
+          <t>17-18 inches</t>
         </is>
       </c>
     </row>
@@ -1320,12 +1320,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'dont_know'}</t>
+          <t>dont_know</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'dont know'}</t>
+          <t>dont know</t>
         </is>
       </c>
     </row>
@@ -1337,12 +1337,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
     </row>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'occasionally'}</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'occasionally'}</t>
+          <t>occasionally</t>
         </is>
       </c>
     </row>
@@ -1371,12 +1371,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'frequently'}</t>
+          <t>frequently</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'frequently'}</t>
+          <t>frequently</t>
         </is>
       </c>
     </row>
@@ -1388,12 +1388,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'all_the_time'}</t>
+          <t>all_the_time</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'all the time'}</t>
+          <t>all the time</t>
         </is>
       </c>
     </row>
@@ -1405,12 +1405,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'never'}</t>
+          <t>never</t>
         </is>
       </c>
     </row>
@@ -1422,12 +1422,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1439,12 +1439,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1456,12 +1456,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'dont_know'}</t>
+          <t>dont_know</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'dont know'}</t>
+          <t>dont know</t>
         </is>
       </c>
     </row>
@@ -1473,12 +1473,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'apple'}</t>
+          <t>apple</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'apple'}</t>
+          <t>apple</t>
         </is>
       </c>
     </row>
@@ -1490,12 +1490,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'dell'}</t>
+          <t>dell</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'dell'}</t>
+          <t>dell</t>
         </is>
       </c>
     </row>
@@ -1507,12 +1507,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'hp'}</t>
+          <t>hp</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'hp'}</t>
+          <t>hp</t>
         </is>
       </c>
     </row>
@@ -1524,12 +1524,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'lenovo'}</t>
+          <t>lenovo</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'lenovo'}</t>
+          <t>lenovo</t>
         </is>
       </c>
     </row>
@@ -1541,12 +1541,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'other'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -1558,12 +1558,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'not_recommended'}</t>
+          <t>not_recommended</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 'not recommended'}</t>
+          <t>not recommended</t>
         </is>
       </c>
     </row>
@@ -1575,12 +1575,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'friend'}</t>
+          <t>friend</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'friend'}</t>
+          <t>friend</t>
         </is>
       </c>
     </row>
@@ -1592,12 +1592,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'family_member'}</t>
+          <t>family_member</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'family member'}</t>
+          <t>family member</t>
         </is>
       </c>
     </row>
@@ -1609,12 +1609,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'colleague'}</t>
+          <t>colleague</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'colleague'}</t>
+          <t>colleague</t>
         </is>
       </c>
     </row>
@@ -1626,12 +1626,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'not_applicable'}</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'not applicable'}</t>
+          <t>not applicable</t>
         </is>
       </c>
     </row>
@@ -1643,12 +1643,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'self'}</t>
+          <t>self</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'self'}</t>
+          <t>self</t>
         </is>
       </c>
     </row>
@@ -1660,12 +1660,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'family_member'}</t>
+          <t>family_member</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'family member'}</t>
+          <t>family member</t>
         </is>
       </c>
     </row>
@@ -1677,12 +1677,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'colleague'}</t>
+          <t>colleague</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'colleague'}</t>
+          <t>colleague</t>
         </is>
       </c>
     </row>
@@ -1694,12 +1694,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'friend'}</t>
+          <t>friend</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'friend'}</t>
+          <t>friend</t>
         </is>
       </c>
     </row>
@@ -1711,12 +1711,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1728,12 +1728,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1745,12 +1745,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'dont_know'}</t>
+          <t>dont_know</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'dont know'}</t>
+          <t>dont know</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1779,12 +1779,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1796,12 +1796,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'maybe'}</t>
+          <t>maybe</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'maybe'}</t>
+          <t>maybe</t>
         </is>
       </c>
     </row>
